--- a/artfynd/A 55263-2021 artfynd.xlsx
+++ b/artfynd/A 55263-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55263-2021 artfynd.xlsx
+++ b/artfynd/A 55263-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3978378</v>
+        <v>71646265</v>
       </c>
       <c r="B2" t="n">
-        <v>99590</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221333</v>
+        <v>101410</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörkö, 150m O om Borg, Srm</t>
+          <t>Borg, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654234.5504448354</v>
+        <v>654237</v>
       </c>
       <c r="R2" t="n">
-        <v>6535946.192944408</v>
+        <v>6536006</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Timmerupplag vid vägkant</t>
+          <t>Gammal dubbelstammig tall i solexponerat söderläga nära väg. Åtgärdsbehov i form av röjning av slånbuskar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,28 +771,133 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3978378</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mörkö, 150m O om Borg, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>654235</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6535946</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mörkö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1995-06-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1995-06-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Timmerupplag vid vägkant</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Lennart Karlén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Lennart Karlén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55263-2021 artfynd.xlsx
+++ b/artfynd/A 55263-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71646265</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,8 +908,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3978378</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>